--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-performer.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-performer.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="231">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -659,6 +659,12 @@
   </si>
   <si>
     <t>CD.translation</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.sdtcSpecialty</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcSpecialty</t>
   </si>
   <si>
     <t>Performer1.assignedEntity.addr</t>
@@ -1034,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK50"/>
+  <dimension ref="A1:AK51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.19140625" customWidth="true" bestFit="true"/>
@@ -5595,11 +5601,9 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5650,7 +5654,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5670,10 +5674,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5696,10 +5700,10 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -5751,7 +5755,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5771,10 +5775,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5785,7 +5789,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>74</v>
@@ -5797,10 +5801,10 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -5852,13 +5856,13 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>74</v>
@@ -5872,10 +5876,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5898,10 +5902,10 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -5953,7 +5957,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -5973,10 +5977,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -5987,7 +5991,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>74</v>
@@ -5999,9 +6003,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="L49" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6052,7 +6058,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6072,10 +6078,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6083,10 +6089,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>74</v>
@@ -6098,7 +6104,7 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>95</v>
+        <v>227</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6154,7 +6160,7 @@
         <v>228</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>75</v>
@@ -6166,6 +6172,105 @@
         <v>74</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK51" t="s" s="2">
         <v>74</v>
       </c>
     </row>
